--- a/data/teams_mapping.xlsx
+++ b/data/teams_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,32 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +58,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,125 +449,1388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Target_Team</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>sap</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SAP Issue</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>SAP_Support</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>login</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Access Issue</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>SAP_Support</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>oracle</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Database_Admin</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>sql</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Database_Admin</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>wifi</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Network</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Network_Ops</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>internet</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Network</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Access Issue</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SAP_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>sso</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Access Issue</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>SAP_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Access Issue</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>SAP_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>access denied</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Access Issue</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>SAP_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>account locked</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Access Issue</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SAP_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>permissions</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Access Issue</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>SAP_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>migration</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>mongodb</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Database_Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>vpn</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>dns</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>firewall</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>bandwidth</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>latency</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ping</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ip address</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>network drive</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Network_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>crash</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>software</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>uninstall</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>patch</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>license</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>activation</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>application</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>outlook</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>teams</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>zoom</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>antivirus</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>malware</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>virus</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Software Issue</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Software_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>laptop</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>keyboard</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>mouse</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>printer</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>scanner</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>headset</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>webcam</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>hard disk</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ram</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>charger</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>usb</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>docking station</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Hardware Issue</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Hardware_Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>aws</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>gcp</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ec2</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>kubernetes</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>docker</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>outage</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>microservice</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Issue</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Cloud_Ops</t>
         </is>
       </c>
     </row>
